--- a/Result/profitability/2020.xlsx
+++ b/Result/profitability/2020.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.50375</v>
+        <v>0.49125</v>
       </c>
       <c r="N2" t="n">
-        <v>16.7875</v>
+        <v>18.125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.42625</v>
+        <v>0.4725</v>
       </c>
       <c r="N3" t="n">
-        <v>16.96625</v>
+        <v>18.265</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.41875</v>
+        <v>0.4225</v>
       </c>
       <c r="N4" t="n">
-        <v>17.0075</v>
+        <v>18.11875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.98</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02750000000000002</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>7.37125</v>
+        <v>8.047499999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006249999999999992</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>6.80625</v>
+        <v>7.5975</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.16875</v>
+        <v>-0.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.862500000000001</v>
+        <v>4.5475</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04250000000000001</v>
+        <v>-0.01500000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>3.717500000000001</v>
+        <v>4.077500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.15875</v>
       </c>
       <c r="N9" t="n">
-        <v>1.436250000000001</v>
+        <v>1.43625</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.06125000000000003</v>
       </c>
       <c r="N11" t="n">
-        <v>1.315000000000001</v>
+        <v>1.315</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.03625000000000002</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8450000000000004</v>
+        <v>0.845</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D75" t="n">
+        <v>770</v>
+      </c>
+      <c r="E75" t="n">
+        <v>259</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="G75" t="n">
+        <v>177</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.17%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>30</v>
+      </c>
+      <c r="J75" t="n">
+        <v>207</v>
+      </c>
+      <c r="K75" t="n">
+        <v>164</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5499999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.880000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1290900941281938</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2735085945399394</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
